--- a/output/pdf_financials_xlsx/CQX.xlsx
+++ b/output/pdf_financials_xlsx/CQX.xlsx
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.207821</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.591596</v>
       </c>
     </row>
     <row r="93">
@@ -2648,7 +2648,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>4.207821</v>
       </c>

--- a/output/pdf_financials_xlsx/CQX.xlsx
+++ b/output/pdf_financials_xlsx/CQX.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.083971</v>
+        <v>0.360975</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.121861</v>
+        <v>1.87525</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.083971</v>
+        <v>-0.360975</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.121861</v>
+        <v>-1.87525</v>
       </c>
     </row>
     <row r="12">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.058252</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.237555</v>
       </c>
     </row>
     <row r="35">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.058252</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.237555</v>
       </c>
     </row>
     <row r="37">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.074382</v>
+        <v>0.01613</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.42639</v>
+        <v>0.188835</v>
       </c>
     </row>
     <row r="49">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2400,7 +2400,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
         <v>0.025</v>
       </c>
@@ -3958,14 +3962,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>-0.360975</v>
+        <v>0.360975</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-1.87525</v>
+        <v>1.87525</v>
       </c>
     </row>
     <row r="64">

--- a/output/pdf_financials_xlsx/CQX.xlsx
+++ b/output/pdf_financials_xlsx/CQX.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.083971</v>
+        <v>0.287616</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.121861</v>
+        <v>0.460335</v>
       </c>
     </row>
     <row r="8">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.000897</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.233785</v>
       </c>
     </row>
     <row r="65">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.039257</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.06539399999999999</v>
       </c>
     </row>
     <row r="68">
@@ -3774,7 +3774,11 @@
           <t>Management and directors' fees 8</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.203645</v>
       </c>
